--- a/Statistics/100m Rygg_statistics.xlsx
+++ b/Statistics/100m Rygg_statistics.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:G212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,12 +821,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kristian Volden</t>
+          <t>Michael Alexander Calder</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.02,32</t>
+          <t>1.02,33</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -834,12 +834,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22.11.2015</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -856,12 +856,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Michael Alexander Calder</t>
+          <t>Kristian Volden</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.02,33</t>
+          <t>1.02,32</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -869,12 +869,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>22.11.2015</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -926,25 +926,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aamund Westermoen</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.02,92</t>
+          <t>1.02,67</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29.09.2018</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -961,25 +961,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Andreas Aglen Alsos</t>
+          <t>Aamund Westermoen</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.03,00</t>
+          <t>1.02,92</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>27.01.2024</t>
+          <t>29.09.2018</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -996,20 +996,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Njål Falch</t>
+          <t>Andreas Aglen Alsos</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.03,10</t>
+          <t>1.03,00</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19.03.2011</t>
+          <t>27.01.2024</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1031,20 +1031,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gleb Eriksson</t>
+          <t>Njål Falch</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.03,87</t>
+          <t>1.03,10</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21.05.2005</t>
+          <t>19.03.2011</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1066,12 +1066,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Emil Vindvik</t>
+          <t>Gleb Eriksson</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.03,85</t>
+          <t>1.03,87</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>21.05.2005</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1101,20 +1101,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jon Olav Båtbukt</t>
+          <t>Emil Vindvik</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.03,95</t>
+          <t>1.03,85</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1136,20 +1136,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Balder Baarholm</t>
+          <t>Jon Olav Båtbukt</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1.04,01</t>
+          <t>1.03,95</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>16.01.2016</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1626,25 +1626,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Leo Petter Hauge Sølvberg</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.07,41</t>
+          <t>1.07,27</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>29.09.2019</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1661,25 +1661,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Brage Flem Habberstad</t>
+          <t>Leo Petter Hauge Sølvberg</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.07,92</t>
+          <t>1.07,41</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11.01.2013</t>
+          <t>29.09.2019</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1696,20 +1696,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Vårin Berge Jensås</t>
+          <t>Brage Flem Habberstad</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.17,30</t>
+          <t>1.07,92</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>16.06.2018</t>
+          <t>11.01.2013</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1731,20 +1731,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Bjørn Eimar Endal Sorteberg</t>
+          <t>Vårin Berge Jensås</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.08,07</t>
+          <t>1.17,30</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>16.06.2018</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1801,12 +1801,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kristoffer Loeng</t>
+          <t>Iris Elise Moen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.08,39</t>
+          <t>1.17,70</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1814,12 +1814,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>03.10.2015</t>
+          <t>19.06.2021</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1836,12 +1836,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Iris Elise Moen</t>
+          <t>Kristoffer Loeng</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.17,70</t>
+          <t>1.08,39</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>19.06.2021</t>
+          <t>03.10.2015</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1906,20 +1906,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Simen Løvås</t>
+          <t>Emmelin Munkhaugen</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.08,75</t>
+          <t>1.16,67</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>23.06.2019</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1941,25 +1941,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jenny Marandon Natvik</t>
+          <t>Simen Løvås</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.18,12</t>
+          <t>1.08,75</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>05.12.2015</t>
+          <t>23.06.2019</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Volda</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1976,25 +1976,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Emmelin Munkhaugen</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.18,18</t>
+          <t>1.08,77</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>25.10.2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2011,25 +2011,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Johan Hjelseth Storstad</t>
+          <t>Jenny Marandon Natvik</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.08,92</t>
+          <t>1.18,12</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>05.12.2015</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Volda</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2046,20 +2046,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Victor Voormolen Gutierrez</t>
+          <t>Johan Hjelseth Storstad</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.09,22</t>
+          <t>1.08,92</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>19.06.2021</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2081,20 +2081,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Torbjørn Ekrem</t>
+          <t>Victor Voormolen Gutierrez</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.09,25</t>
+          <t>1.09,22</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>29.03.2025</t>
+          <t>19.06.2021</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2116,12 +2116,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Morten Olden Larsen</t>
+          <t>Torbjørn Ekrem</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.09,29</t>
+          <t>1.09,25</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20.06.2015</t>
+          <t>29.03.2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2151,25 +2151,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Arnt Martin Ystenes</t>
+          <t>Morten Olden Larsen</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.09,57</t>
+          <t>1.09,29</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>27.10.2012</t>
+          <t>20.06.2015</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2186,25 +2186,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Hans Ourson Liem</t>
+          <t>Arnt Martin Ystenes</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.09,62</t>
+          <t>1.09,57</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>04.12.2022</t>
+          <t>27.10.2012</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2221,25 +2221,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ole Skuseth</t>
+          <t>Hans Ourson Liem</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.09,76</t>
+          <t>1.09,62</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19.11.2022</t>
+          <t>04.12.2022</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2256,12 +2256,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sander Haugan</t>
+          <t>Ole Skuseth</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.09,74</t>
+          <t>1.09,76</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>19.11.2022</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2291,20 +2291,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ole Andreas Alsos</t>
+          <t>Sander Haugan</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.09,88</t>
+          <t>1.09,74</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>10.04.2016</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2326,12 +2326,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kjersti Skauge Bysting</t>
+          <t>Ole Andreas Alsos</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.19,37</t>
+          <t>1.09,88</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>24.06.2007</t>
+          <t>10.04.2016</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2361,25 +2361,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Jonas Fiskaa Barstad</t>
+          <t>Kjersti Skauge Bysting</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.10,03</t>
+          <t>1.19,37</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>24.06.2007</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2396,25 +2396,25 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sindre Søderlund</t>
+          <t>Jonas Fiskaa Barstad</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.10,22</t>
+          <t>1.10,03</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>04.10.2008</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2431,25 +2431,25 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Aksel Viken Refseth</t>
+          <t>Sindre Søderlund</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.10,55</t>
+          <t>1.10,22</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>04.10.2008</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2466,25 +2466,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Joakim Gjerde</t>
+          <t>Aksel Viken Refseth</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.10,60</t>
+          <t>1.10,55</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>08.10.2016</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2501,12 +2501,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Simon Perssønn Mørseth</t>
+          <t>Joakim Gjerde</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.10,62</t>
+          <t>1.10,60</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>08.10.2016</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2536,20 +2536,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Thomas Johansen</t>
+          <t>Simon Perssønn Mørseth</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.10,80</t>
+          <t>1.10,62</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>01.11.2014</t>
+          <t>18.01.2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2571,12 +2571,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Robert Tellefsen</t>
+          <t>Thomas Johansen</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.10,75</t>
+          <t>1.10,80</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>03.03.2018</t>
+          <t>01.11.2014</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2606,12 +2606,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Henning Andersson</t>
+          <t>Robert Tellefsen</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1.10,80</t>
+          <t>1.10,75</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>17.01.2015</t>
+          <t>03.03.2018</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2641,25 +2641,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sondre Furmyr Johansen</t>
+          <t>Henning Andersson</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.11,03</t>
+          <t>1.10,80</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>23.10.2022</t>
+          <t>17.01.2015</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2676,25 +2676,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lucas Nachappa Muthanna</t>
+          <t>Sondre Furmyr Johansen</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.11,39</t>
+          <t>1.11,03</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>23.10.2022</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3271,12 +3271,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Thomas Stur Ekrem</t>
+          <t>Sondre Brunvoll Møllerløkken</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1.15,56</t>
+          <t>1.15,59</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>15.02.2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3306,12 +3306,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sondre Brunvoll Møllerløkken</t>
+          <t>Thomas Stur Ekrem</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1.15,59</t>
+          <t>1.15,56</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>18.01.2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3341,12 +3341,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Jonas D. Lesund</t>
+          <t>Lin Carola Magdalene Nygren</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.16,31</t>
+          <t>1.25,27</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>15.09.2013</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3376,12 +3376,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Manith Randula Attanapola</t>
+          <t>Jonas D. Lesund</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1.16,23</t>
+          <t>1.16,31</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>16.10.2011</t>
+          <t>15.09.2013</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Brunflo</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3411,25 +3411,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Vegard Skjervold</t>
+          <t>Manith Randula Attanapola</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1.16,83</t>
+          <t>1.16,23</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>29.09.2018</t>
+          <t>16.10.2011</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Brunflo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3446,25 +3446,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Oliver Grøtte Ramstad</t>
+          <t>Vegard Skjervold</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1.17,31</t>
+          <t>1.16,83</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>29.09.2018</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3481,20 +3481,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Eilert Juul Wolfgang</t>
+          <t>Oliver Grøtte Ramstad</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1.17,35</t>
+          <t>1.17,31</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>05.10.2013</t>
+          <t>26.04.2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3516,20 +3516,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Jakob Isaksen</t>
+          <t>Eilert Juul Wolfgang</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1.17,60</t>
+          <t>1.17,35</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>19.11.2022</t>
+          <t>05.10.2013</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3551,20 +3551,20 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Alfred Fenstad Høysæter</t>
+          <t>Jakob Isaksen</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1.17,84</t>
+          <t>1.17,60</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>19.11.2022</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3586,20 +3586,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Daniel Moen Manriquez</t>
+          <t>Alfred Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1.18,04</t>
+          <t>1.17,84</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>31.10.2015</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3621,25 +3621,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Vegard Maaø</t>
+          <t>Edvard Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1.18,10</t>
+          <t>1.17,85</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>05.12.2009</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3656,25 +3656,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Gunnleif Nielsen</t>
+          <t>Daniel Moen Manriquez</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1.18,27</t>
+          <t>1.18,04</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>03.03.2018</t>
+          <t>31.10.2015</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3691,25 +3691,25 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Bjørnar Bakkejord</t>
+          <t>Vegard Maaø</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1.18,66</t>
+          <t>1.18,10</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>18.09.2005</t>
+          <t>05.12.2009</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3726,25 +3726,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Eirik Hamnes Ulriksen</t>
+          <t>Gunnleif Nielsen</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1.18,97</t>
+          <t>1.18,27</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>03.03.2018</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3761,25 +3761,25 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ask Yifei Baldersheim</t>
+          <t>Bjørnar Bakkejord</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1.19,03</t>
+          <t>1.18,66</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>24.10.2020</t>
+          <t>18.09.2005</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3796,20 +3796,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sigurd Rodal Leirgulen</t>
+          <t>Eirik Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1.19,21</t>
+          <t>1.18,97</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3831,25 +3831,25 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Erlend Søderlund</t>
+          <t>Ask Yifei Baldersheim</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1.19,35</t>
+          <t>1.19,03</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>16.10.2011</t>
+          <t>24.10.2020</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Brunflo</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3866,20 +3866,20 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Pedro Manquehual</t>
+          <t>Sigurd Rodal Leirgulen</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1.19,55</t>
+          <t>1.19,21</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3901,20 +3901,20 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Edvard Hamnes Ulriksen</t>
+          <t>Edvin Grenne Spangelo</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1.19,69</t>
+          <t>1.19,38</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3936,25 +3936,25 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Ingjerd Jepsen Vegge</t>
+          <t>Erlend Søderlund</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1.30,66</t>
+          <t>1.19,35</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20.01.2012</t>
+          <t>16.10.2011</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Brunflo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3971,20 +3971,20 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Ivan Erikovitch Alvestad</t>
+          <t>Pedro Manquehual</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1.20,54</t>
+          <t>1.19,55</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>26.04.2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4006,25 +4006,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Paal Aagaard</t>
+          <t>Ingjerd Jepsen Vegge</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1.20,53</t>
+          <t>1.30,66</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>01.04.2006</t>
+          <t>20.01.2012</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lambertseter</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4041,20 +4041,20 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Lin Carola Magdalene Nygren</t>
+          <t>Ivan Erikovitch Alvestad</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1.31,78</t>
+          <t>1.20,54</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4076,25 +4076,25 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Bjørn Erik Ystenes</t>
+          <t>Paal Aagaard</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1.20,82</t>
+          <t>1.20,53</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>11.01.2013</t>
+          <t>01.04.2006</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Lambertseter</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4111,25 +4111,25 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Vegard S. Wigum</t>
+          <t>Bjørn Erik Ystenes</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1.20,97</t>
+          <t>1.20,82</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>23.11.2013</t>
+          <t>11.01.2013</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4146,25 +4146,25 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Jon Noé Høye</t>
+          <t>Vegard S. Wigum</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1.21,16</t>
+          <t>1.20,97</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>23.11.2013</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4181,25 +4181,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Anton Sergeevich Gorodkov</t>
+          <t>Jon Noé Høye</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1.21,46</t>
+          <t>1.21,16</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>06.12.2015</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4216,25 +4216,25 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Finn Øivind Fevang</t>
+          <t>Anton Sergeevich Gorodkov</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1.21,72</t>
+          <t>1.21,46</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>19.03.2006</t>
+          <t>06.12.2015</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4251,12 +4251,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Edvin Grenne Spangelo</t>
+          <t>Finn Øivind Fevang</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1.21,79</t>
+          <t>1.21,72</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>19.03.2006</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4356,12 +4356,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>David Fjeld</t>
+          <t>Håkon Johansen</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1.22,61</t>
+          <t>1.22,52</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20.10.2007</t>
+          <t>18.09.2005</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4391,12 +4391,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Håkon Johansen</t>
+          <t>David Fjeld</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1.22,52</t>
+          <t>1.22,61</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>18.09.2005</t>
+          <t>20.10.2007</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4426,25 +4426,25 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Trond Klakken</t>
+          <t>Rasmus Larsen Natvig</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1.23,10</t>
+          <t>1.22,86</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4461,20 +4461,20 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Johan Mostervik</t>
+          <t>Trond Klakken</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1.23,86</t>
+          <t>1.23,10</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20.01.2018</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4496,20 +4496,20 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Lyder Ringsvold Hogstad</t>
+          <t>Philip Giske Nyman</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1.23,89</t>
+          <t>1.23,59</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>19.01.2019</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4531,20 +4531,20 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Morten Schanke</t>
+          <t>Ellen Kristine Eidsmo Hova</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1.24,03</t>
+          <t>1.33,45</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>10.04.2016</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4566,20 +4566,20 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Njål Høie</t>
+          <t>Lyder Ringsvold Hogstad</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1.24,30</t>
+          <t>1.23,89</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>14.09.2014</t>
+          <t>19.01.2019</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4601,25 +4601,25 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Tony Christopher Moflag</t>
+          <t>Johan Mostervik</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1.24,33</t>
+          <t>1.23,86</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>25.03.2006</t>
+          <t>20.01.2018</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4636,20 +4636,20 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Kristian Myhr Høgstøl</t>
+          <t>Morten Schanke</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1.24,22</t>
+          <t>1.24,03</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>10.04.2016</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4671,12 +4671,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Bjarne Forfot</t>
+          <t>Gunhild Furuholt Valle</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1.24,28</t>
+          <t>1.35,73</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>30.09.2017</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4706,12 +4706,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Gunhild Furuholt Valle</t>
+          <t>Bjarne Forfot</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1.35,73</t>
+          <t>1.24,28</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>30.09.2017</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4741,20 +4741,20 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Brage Gylseth Dahl</t>
+          <t>Kristian Myhr Høgstøl</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1.24,52</t>
+          <t>1.24,22</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -4776,20 +4776,20 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Tor Arne Hegvik</t>
+          <t>Njål Høie</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1.24,75</t>
+          <t>1.24,30</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>05.02.2006</t>
+          <t>14.09.2014</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4811,25 +4811,25 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ailin Østerås</t>
+          <t>Tony Christopher Moflag</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1.36,48</t>
+          <t>1.24,33</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>18.06.2011</t>
+          <t>25.03.2006</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4846,20 +4846,20 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Isabel Ødegård Pedersen</t>
+          <t>Brage Gylseth Dahl</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1.36,68</t>
+          <t>1.24,52</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4881,25 +4881,25 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Christian Dahle-Øfsti</t>
+          <t>Tor Arne Hegvik</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1.25,18</t>
+          <t>1.24,75</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>01.06.2013</t>
+          <t>05.02.2006</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4916,20 +4916,20 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Anton Hoel</t>
+          <t>Ailin Østerås</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1.25,93</t>
+          <t>1.36,48</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>15.09.2013</t>
+          <t>18.06.2011</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4951,25 +4951,25 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Ingeborg Strandenes</t>
+          <t>Isabel Ødegård Pedersen</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1.38,00</t>
+          <t>1.36,68</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4986,25 +4986,25 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Daniel Stanislaw Czuba</t>
+          <t>Christian Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1.26,72</t>
+          <t>1.25,18</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>01.06.2013</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5021,20 +5021,20 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Conrad Sippala Hassel</t>
+          <t>Anton Hoel</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1.26,59</t>
+          <t>1.25,93</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>15.09.2013</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5056,25 +5056,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Leander Gisvold Restad</t>
+          <t>Ingeborg Strandenes</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1.27,07</t>
+          <t>1.38,00</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>27.04.2019</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5091,25 +5091,25 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Dhanushi Attanapola</t>
+          <t>Daniel Stanislaw Czuba</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1.38,83</t>
+          <t>1.26,72</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20.06.2009</t>
+          <t>15.02.2025</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5126,25 +5126,25 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Daniel Haugen Ngwenya</t>
+          <t>Conrad Sippala Hassel</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1.29,00</t>
+          <t>1.26,59</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>20.10.2007</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5161,25 +5161,25 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Henrik Vaaler</t>
+          <t>Leander Gisvold Restad</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1.28,89</t>
+          <t>1.27,07</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>27.04.2019</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5196,20 +5196,20 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Fredrik Holberg</t>
+          <t>Dhanushi Attanapola</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1.28,89</t>
+          <t>1.38,83</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>20.06.2009</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5236,20 +5236,20 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1.41,19</t>
+          <t>1.38,44</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5266,25 +5266,25 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Magnus Svindland Næsgaard</t>
+          <t>Daniel Haugen Ngwenya</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1.29,28</t>
+          <t>1.29,00</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>14.01.2023</t>
+          <t>20.10.2007</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5301,25 +5301,25 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>David Csejtey</t>
+          <t>Henrik Vaaler</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1.30,72</t>
+          <t>1.28,89</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>29.09.2019</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5336,20 +5336,20 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Thomas Paulsen</t>
+          <t>Fredrik Holberg</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1.30,83</t>
+          <t>1.28,89</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>17.01.2014</t>
+          <t>08.12.2024</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5371,25 +5371,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Ellen Kristine Eidsmo Hova</t>
+          <t>Magnus Svindland Næsgaard</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1.43,64</t>
+          <t>1.29,28</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>01.12.2024</t>
+          <t>14.01.2023</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5406,25 +5406,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Magnus Bakkejord</t>
+          <t>Olav Høyland Hofstad</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1.31,60</t>
+          <t>1.30,43</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>16.10.2011</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Brunflo</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5441,25 +5441,25 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>William Johannes Kirkelund Kristiansen</t>
+          <t>David Csejtey</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1.31,99</t>
+          <t>1.30,72</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>14.01.2023</t>
+          <t>29.09.2019</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5476,20 +5476,20 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Rasmus Larsen Natvig</t>
+          <t>Thomas Paulsen</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1.32,28</t>
+          <t>1.30,83</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>17.01.2014</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5511,25 +5511,25 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sondre Thorgaard</t>
+          <t>Magnus Bakkejord</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1.33,18</t>
+          <t>1.31,60</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>16.10.2011</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Brunflo</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5546,20 +5546,20 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>William Wale</t>
+          <t>William Johannes Kirkelund Kristiansen</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1.33,51</t>
+          <t>1.31,99</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>14.09.2014</t>
+          <t>14.01.2023</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5581,25 +5581,25 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Oscar Kvaløy Tiller</t>
+          <t>Cornelius Wik</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1.33,91</t>
+          <t>1.32,32</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>23.10.2021</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5616,20 +5616,20 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Arild Håkonsen Stixrud</t>
+          <t>Sondre Thorgaard</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1.33,98</t>
+          <t>1.33,18</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5651,25 +5651,25 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Philip Giske Nyman</t>
+          <t>William Wale</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1.34,39</t>
+          <t>1.33,51</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>19.10.2024</t>
+          <t>14.09.2014</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5686,25 +5686,25 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Eirik Ingeberg Garshol</t>
+          <t>Oscar Kvaløy Tiller</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1.36,81</t>
+          <t>1.33,91</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>27.01.2024</t>
+          <t>23.10.2021</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5721,20 +5721,20 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Marit Søberg</t>
+          <t>Arild Håkonsen Stixrud</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1.50,28</t>
+          <t>1.33,98</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20.06.2009</t>
+          <t>26.04.2025</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -5756,20 +5756,20 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Liem Emily Liv</t>
+          <t>Eirik Ingeberg Garshol</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1.51,50</t>
+          <t>1.36,81</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20.05.2017</t>
+          <t>27.01.2024</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5791,20 +5791,20 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Jakob M. Tjøstheim</t>
+          <t>Marit Søberg</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1.38,62</t>
+          <t>1.50,28</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>15.09.2013</t>
+          <t>20.06.2009</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5826,25 +5826,25 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Iselin Græsli Skaret</t>
+          <t>Liem Emily Liv</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1.52,70</t>
+          <t>1.51,50</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>27.04.2019</t>
+          <t>20.05.2017</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5861,16 +5861,16 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Einar Risholt Moen</t>
+          <t>Jakob M. Tjøstheim</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1.39,63</t>
+          <t>1.38,62</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -5896,25 +5896,25 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Anniken Skjøstad</t>
+          <t>Iselin Græsli Skaret</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1.53,30</t>
+          <t>1.52,70</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>27.04.2019</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5931,20 +5931,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Robin von Bargen</t>
+          <t>Einar Risholt Moen</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1.40,13</t>
+          <t>1.39,63</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>21.06.2008</t>
+          <t>15.09.2013</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5966,20 +5966,20 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Leo Alexander Farias Kristiansen</t>
+          <t>Anniken Skjøstad</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1.40,52</t>
+          <t>1.53,30</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6001,20 +6001,20 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Randi Leiknes</t>
+          <t>Robin von Bargen</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1.54,19</t>
+          <t>1.40,13</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>24.05.2008</t>
+          <t>21.06.2008</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6036,20 +6036,20 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Setareh Kulsum Sigrid Feyzi</t>
+          <t>Leo Alexander Farias Kristiansen</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1.54,47</t>
+          <t>1.40,52</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>16.09.2017</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6071,20 +6071,20 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Erik Solbakken Andersen</t>
+          <t>Randi Leiknes</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1.40,94</t>
+          <t>1.54,19</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>24.05.2008</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6106,20 +6106,20 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Angelico Mikkel Andersen</t>
+          <t>Setareh Kulsum Sigrid Feyzi</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>1.41,72</t>
+          <t>1.54,47</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>16.09.2017</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6141,20 +6141,20 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Vår Kristine Sollien Skar</t>
+          <t>Erik Solbakken Andersen</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1.55,44</t>
+          <t>1.40,94</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>17.01.2014</t>
+          <t>18.01.2025</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6176,20 +6176,20 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Mateo Joseph Barriet</t>
+          <t>Vår Kristine Sollien Skar</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1.41,89</t>
+          <t>1.55,44</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>17.01.2014</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6211,25 +6211,25 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>August Sivertsen Nestgaard</t>
+          <t>Angelico Mikkel Andersen</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1.42,16</t>
+          <t>1.41,72</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>18.11.2017</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6246,25 +6246,25 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Marcus Thalberg Fagerheim</t>
+          <t>Mateo Joseph Barriet</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1.42,38</t>
+          <t>1.41,89</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>12.11.2011</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6281,25 +6281,25 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Magnus Hestvik Larsen</t>
+          <t>Marcus Thalberg Fagerheim</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1.43,33</t>
+          <t>1.42,38</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>18.04.2009</t>
+          <t>12.11.2011</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6316,25 +6316,25 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Filip Dalsaune</t>
+          <t>August Sivertsen Nestgaard</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>1.43,45</t>
+          <t>1.42,16</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>18.11.2017</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6351,25 +6351,25 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Olav Høyland Hofstad</t>
+          <t>Magnus Hestvik Larsen</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>1.44,04</t>
+          <t>1.43,33</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>18.04.2009</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6386,25 +6386,25 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ingvar Høgås Wik</t>
+          <t>Filip Dalsaune</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>1.43,88</t>
+          <t>1.43,45</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>14.03.2015</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6421,25 +6421,25 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Morten Johansen</t>
+          <t>Ingvar Høgås Wik</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>1.45,16</t>
+          <t>1.43,88</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>08.10.2005</t>
+          <t>14.03.2015</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6456,20 +6456,20 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>André Prestmo-Edvardsen</t>
+          <t>Morten Johansen</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1.45,61</t>
+          <t>1.45,16</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>08.10.2005</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6496,15 +6496,15 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>1.45,57</t>
+          <t>1.45,55</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6526,20 +6526,20 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Bernard Smuk</t>
+          <t>André Prestmo-Edvardsen</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1.46,46</t>
+          <t>1.45,61</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>27.04.2024</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6561,20 +6561,20 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Elias Lien</t>
+          <t>Bernard Smuk</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1.46,75</t>
+          <t>1.46,46</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>16.06.2018</t>
+          <t>27.04.2024</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6596,20 +6596,20 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Jesper Øvermo Johansen</t>
+          <t>Elias Lien</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1.47,48</t>
+          <t>1.46,75</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>16.06.2018</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6631,20 +6631,20 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Theo Sjøhelle</t>
+          <t>Mikkel Fenstad</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1.50,69</t>
+          <t>1.46,76</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -6666,20 +6666,20 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Cornelius Wik</t>
+          <t>Jesper Øvermo Johansen</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1.51,00</t>
+          <t>1.47,48</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>12.11.2023</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -6701,20 +6701,20 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Tymofii Dzisiak</t>
+          <t>Ingeborg Vold Kirkvold</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1.52,08</t>
+          <t>2.00,76</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -6736,25 +6736,25 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Peder Lund Juul</t>
+          <t>Emil Falkenbo-Skalmerås</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1.51,91</t>
+          <t>1.48,74</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>02.04.2022</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6771,20 +6771,20 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Agnes Agersborg</t>
+          <t>Lilly Fludal Osland</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2.07,21</t>
+          <t>2.02,96</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>10.10.2009</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -6806,25 +6806,25 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Eirik Solligård</t>
+          <t>Theo Sjøhelle</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>1.52,69</t>
+          <t>1.50,69</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>18.04.2009</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6841,20 +6841,20 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Debik Isabella Johanne</t>
+          <t>Agnes Agersborg</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2.10,29</t>
+          <t>2.07,21</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>15.09.2018</t>
+          <t>10.10.2009</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6876,20 +6876,20 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Nataniel Skjøndal-Bar</t>
+          <t>Tymofii Dzisiak</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>1.55,39</t>
+          <t>1.52,08</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>23.06.2019</t>
+          <t>26.04.2025</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6911,25 +6911,25 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Henrik Sumstad</t>
+          <t>Peder Lund Juul</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1.56,20</t>
+          <t>1.51,91</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>27.10.2012</t>
+          <t>02.04.2022</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6946,25 +6946,25 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Nikan Ommani</t>
+          <t>Eirik Solligård</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>1.56,63</t>
+          <t>1.52,69</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>18.04.2009</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6981,20 +6981,20 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Dominic Olav Sollien-Pearn</t>
+          <t>Debik Isabella Johanne</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>1.57,62</t>
+          <t>2.10,29</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>19.06.2021</t>
+          <t>15.09.2018</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -7016,20 +7016,20 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Markus Indergård Holm</t>
+          <t>Nataniel Skjøndal-Bar</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>1.57,89</t>
+          <t>1.55,39</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>24.05.2008</t>
+          <t>23.06.2019</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7051,25 +7051,25 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Mikkel Fenstad</t>
+          <t>Henrik Sumstad</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>1.58,17</t>
+          <t>1.56,20</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>10.02.2024</t>
+          <t>27.10.2012</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7086,20 +7086,20 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Ingeborg Vold Kirkvold</t>
+          <t>Nikan Ommani</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2.14,86</t>
+          <t>1.56,63</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -7121,20 +7121,20 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Håkon Emil Øien</t>
+          <t>Dominic Olav Sollien-Pearn</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>1.58,72</t>
+          <t>1.57,62</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>29.10.2011</t>
+          <t>19.06.2021</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -7156,20 +7156,20 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Elias Andersson</t>
+          <t>Markus Indergård Holm</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2.00,14</t>
+          <t>1.57,89</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>14.09.2014</t>
+          <t>24.05.2008</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -7191,20 +7191,20 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Sigurd Øie Seland</t>
+          <t>Håkon Emil Øien</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2.00,54</t>
+          <t>1.58,72</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>30.09.2023</t>
+          <t>29.10.2011</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -7226,20 +7226,20 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Gajithsing Ajeethsing</t>
+          <t>Elias Andersson</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2.02,43</t>
+          <t>2.00,14</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>14.09.2014</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -7261,20 +7261,20 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Magnus Hope</t>
+          <t>Sigurd Øie Seland</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2.02,85</t>
+          <t>2.00,54</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>30.09.2023</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -7296,20 +7296,20 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Hans Otto Søyseth</t>
+          <t>Noah Kvam Haaheim</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2.06,94</t>
+          <t>2.00,98</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20.06.2015</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -7331,25 +7331,25 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Fredrik Hårsaker Myrenget</t>
+          <t>Barnaby Lee_Wright</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2.08,08</t>
+          <t>2.01,70</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>21.04.2018</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7366,20 +7366,20 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Theodor Hoff</t>
+          <t>Gajithsing Ajeethsing</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2.08,27</t>
+          <t>2.02,43</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>11.01.2013</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -7401,20 +7401,20 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Jørgen Norvik Skeide</t>
+          <t>Magnus Hope</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2.09,81</t>
+          <t>2.02,85</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>08.10.2005</t>
+          <t>09.11.2024</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -7436,25 +7436,25 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Jo Svendsen</t>
+          <t>Brage Hetling</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2.10,18</t>
+          <t>2.05,27</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>29.09.2019</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7471,25 +7471,25 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Jesper Julius Sundseth Skjærli</t>
+          <t>Hans Otto Søyseth</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2.10,57</t>
+          <t>2.06,94</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>19.10.2024</t>
+          <t>20.06.2015</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7506,25 +7506,25 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Alexander Andersen</t>
+          <t>Fredrik Hårsaker Myrenget</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2.13,66</t>
+          <t>2.08,08</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>02.11.2013</t>
+          <t>21.04.2018</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7541,20 +7541,20 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Aleksander Belsvik Skarbø</t>
+          <t>Theodor Hoff</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2.14,73</t>
+          <t>2.08,27</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>11.01.2013</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -7576,20 +7576,20 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Riccardo Manum</t>
+          <t>Jørgen Norvik Skeide</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2.24,54</t>
+          <t>2.09,81</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>27.04.2024</t>
+          <t>08.10.2005</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -7611,25 +7611,25 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Isak Andrè Rausandhaug-Rise</t>
+          <t>Jo Svendsen</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2.36,25</t>
+          <t>2.10,18</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>24.10.2020</t>
+          <t>29.09.2019</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7646,33 +7646,208 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
+          <t>Jesper Julius Sundseth Skjærli</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2.10,57</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>50</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>19.10.2024</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Alexander Andersen</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2.13,66</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>47</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>02.11.2013</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Aleksander Belsvik Skarbø</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2.14,73</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>46</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>17.11.2019</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Riccardo Manum</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2.24,54</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>37</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>27.04.2024</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Isak Andrè Rausandhaug-Rise</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2.36,25</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>29</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>24.10.2020</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
           <t>Casper Dahle-Øfsti</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>2.35,68</t>
         </is>
       </c>
-      <c r="C207" t="n">
+      <c r="C212" t="n">
         <v>29</v>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>15.09.2013</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>Trondheim</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -8712,12 +8887,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sondre Furmyr Johansen</t>
+          <t>Jonas Fiskaa Barstad</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.13,98</t>
+          <t>1.14,00</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -8725,12 +8900,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19.06.2022</t>
+          <t>26.06.2015</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -8747,12 +8922,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jonas Fiskaa Barstad</t>
+          <t>Sondre Furmyr Johansen</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.14,00</t>
+          <t>1.13,98</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -8760,12 +8935,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26.06.2015</t>
+          <t>19.06.2022</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9552,12 +9727,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Edvard Hamnes Ulriksen</t>
+          <t>Kristoffer Loeng</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.20,65</t>
+          <t>1.20,67</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -9565,12 +9740,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>14.06.2025</t>
+          <t>05.07.2013</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -9587,12 +9762,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kristoffer Loeng</t>
+          <t>Edvard Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.20,67</t>
+          <t>1.20,65</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -9600,12 +9775,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>05.07.2013</t>
+          <t>14.06.2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -9762,12 +9937,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jonas D. Lesund</t>
+          <t>Sondre Grimsmo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.22,81</t>
+          <t>1.22,91</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -9775,7 +9950,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>13.04.2013</t>
+          <t>26.04.2008</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -9797,12 +9972,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sondre Grimsmo</t>
+          <t>Jonas D. Lesund</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.22,91</t>
+          <t>1.22,81</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -9810,7 +9985,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>26.04.2008</t>
+          <t>13.04.2013</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -11100,7 +11275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:G194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11148,20 +11323,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.02,79</t>
+          <t>1.00,47</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>668</v>
+        <v>712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.11.2024</t>
+          <t>15.11.2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bodø</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -12298,12 +12473,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Anita Klungervik</t>
+          <t>Andrea Lintorp</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.15,24</t>
+          <t>1.15,23</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -12311,12 +12486,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>27.01.2024</t>
+          <t>26.10.2013</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -12333,12 +12508,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Andrea Lintorp</t>
+          <t>Anita Klungervik</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.15,23</t>
+          <t>1.15,24</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -12346,12 +12521,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>26.10.2013</t>
+          <t>27.01.2024</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -12438,25 +12613,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Maria Bøe</t>
+          <t>Silje Pettersen Olden</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.15,91</t>
+          <t>1.14,59</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>09.10.2010</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -12473,12 +12648,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Anne Bostad Hegvold</t>
+          <t>Maria Bøe</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.15,90</t>
+          <t>1.15,91</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -12486,12 +12661,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13.03.2010</t>
+          <t>09.10.2010</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -12508,25 +12683,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Vilde Austmo</t>
+          <t>Anne Bostad Hegvold</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.16,24</t>
+          <t>1.15,90</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20.01.2018</t>
+          <t>13.03.2010</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -12578,25 +12753,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Camilla Dahle-Øfsti</t>
+          <t>Vilde Austmo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.16,37</t>
+          <t>1.16,24</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>21.03.2015</t>
+          <t>20.01.2018</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -12613,25 +12788,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Malin Schanke Tømmervik</t>
+          <t>Camilla Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.16,72</t>
+          <t>1.16,37</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>06.03.2010</t>
+          <t>21.03.2015</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12648,25 +12823,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Helle Krogstad</t>
+          <t>Malin Schanke Tømmervik</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.17,17</t>
+          <t>1.16,72</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20.10.2007</t>
+          <t>06.03.2010</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lambertseter</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -12683,25 +12858,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Aurora Moen Wannebo</t>
+          <t>Helle Krogstad</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.17,26</t>
+          <t>1.17,17</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>01.11.2014</t>
+          <t>20.10.2007</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Lambertseter</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -12753,20 +12928,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Silje Aadahl</t>
+          <t>Aurora Moen Wannebo</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.17,32</t>
+          <t>1.17,26</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>16.09.2017</t>
+          <t>01.11.2014</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -12788,12 +12963,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nora Kristine Rasmussen</t>
+          <t>Silje Aadahl</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.17,37</t>
+          <t>1.17,32</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -12801,7 +12976,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20.06.2015</t>
+          <t>16.09.2017</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -12823,20 +12998,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lisa Ling Klauseth Liasjø</t>
+          <t>Nora Kristine Rasmussen</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.17,48</t>
+          <t>1.17,37</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>20.06.2015</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -12858,25 +13033,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cesilie Solberg Jørgensen</t>
+          <t>Lisa Ling Klauseth Liasjø</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.17,84</t>
+          <t>1.17,48</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>26.05.2013</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Slåtthaughallen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -12893,25 +13068,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hedda Fosseng Traa</t>
+          <t>Cesilie Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.18,50</t>
+          <t>1.17,84</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>17.01.2015</t>
+          <t>26.05.2013</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Slåtthaughallen</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -12928,12 +13103,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Torborg Duesten Blokkum</t>
+          <t>Hedda Fosseng Traa</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.18,52</t>
+          <t>1.18,50</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -12941,12 +13116,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>08.03.2013</t>
+          <t>17.01.2015</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stord</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -12963,25 +13138,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marthe Kalvik</t>
+          <t>Torborg Duesten Blokkum</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.18,57</t>
+          <t>1.18,52</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>25.01.2008</t>
+          <t>08.03.2013</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stord</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -12998,25 +13173,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Hedda Østgaard</t>
+          <t>Marthe Kalvik</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.18,86</t>
+          <t>1.18,57</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>07.05.2010</t>
+          <t>25.01.2008</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -13033,12 +13208,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Silje Pettersen Olden</t>
+          <t>Hedda Østgaard</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.18,87</t>
+          <t>1.18,86</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -13046,12 +13221,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>05.12.2021</t>
+          <t>07.05.2010</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -13488,12 +13663,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Hege Solberg Jørgensen</t>
+          <t>Thea Lervold Høffler</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1.21,08</t>
+          <t>1.21,06</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -13501,12 +13676,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>08.10.2016</t>
+          <t>20.06.2015</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13558,12 +13733,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Thea Lervold Høffler</t>
+          <t>Hege Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1.21,06</t>
+          <t>1.21,08</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -13571,12 +13746,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>20.06.2015</t>
+          <t>08.10.2016</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13593,20 +13768,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sunniva Belsnes</t>
+          <t>Alexandra Contreras Jimenez</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1.21,11</t>
+          <t>1.19,78</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16.06.2018</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -13628,20 +13803,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Oline Skjønberg</t>
+          <t>Sunniva Belsnes</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1.21,22</t>
+          <t>1.21,11</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>16.06.2018</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -13663,25 +13838,25 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Heidi Elisabeth Ysland</t>
+          <t>Oline Skjønberg</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1.21,44</t>
+          <t>1.21,22</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>04.12.2016</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13698,12 +13873,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Erika Nicole Hagen</t>
+          <t>Heidi Elisabeth Ysland</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1.21,41</t>
+          <t>1.21,44</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -13711,12 +13886,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>12.02.2022</t>
+          <t>04.12.2016</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -13733,12 +13908,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Oda Sem Austmo</t>
+          <t>Erika Nicole Hagen</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1.21,37</t>
+          <t>1.21,41</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -13746,12 +13921,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>04.10.2014</t>
+          <t>12.02.2022</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -13768,20 +13943,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Nina Alicja Skarø</t>
+          <t>Oda Sem Austmo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1.21,72</t>
+          <t>1.21,37</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>19.01.2019</t>
+          <t>04.10.2014</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -13803,25 +13978,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Dorottya Csejtey</t>
+          <t>Nina Alicja Skarø</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1.21,73</t>
+          <t>1.21,72</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>18.11.2017</t>
+          <t>19.01.2019</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -13873,25 +14048,25 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Linn Amalie Aresvik</t>
+          <t>Dorottya Csejtey</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1.21,85</t>
+          <t>1.21,73</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>06.10.2012</t>
+          <t>18.11.2017</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -13908,20 +14083,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alexandra Contreras Jimenez</t>
+          <t>Linn Amalie Aresvik</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1.22,14</t>
+          <t>1.21,85</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>09.11.2024</t>
+          <t>06.10.2012</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -14328,12 +14503,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Frida Pauline Busch</t>
+          <t>Silje Dahle</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1.24,62</t>
+          <t>1.24,66</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -14341,12 +14516,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>20.10.2018</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -14363,12 +14538,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Silje Dahle</t>
+          <t>Frida Pauline Busch</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1.24,66</t>
+          <t>1.24,62</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -14376,12 +14551,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>20.10.2018</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -14608,12 +14783,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Alisa Kulagina</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1.27,09</t>
+          <t>1.25,64</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -14621,12 +14796,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20.06.2015</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -14643,25 +14818,25 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Olivia Sterud Prytz</t>
+          <t>Othelie Annette Høie</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1.27,19</t>
+          <t>1.27,09</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>27.04.2019</t>
+          <t>20.06.2015</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -14678,25 +14853,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sofie Hoff</t>
+          <t>Olivia Sterud Prytz</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1.27,32</t>
+          <t>1.27,19</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>27.04.2019</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -14713,20 +14888,20 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Gudrun Berg Ildstad</t>
+          <t>Sofie Hoff</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1.27,46</t>
+          <t>1.27,32</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>08.10.2005</t>
+          <t>18.01.2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -14748,12 +14923,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Marthe Eline Waagø-Hansen</t>
+          <t>Gudrun Berg Ildstad</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1.27,45</t>
+          <t>1.27,46</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -14761,7 +14936,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>08.10.2005</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -14783,12 +14958,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Isabella Johanne Debik</t>
+          <t>Marthe Eline Waagø-Hansen</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1.27,48</t>
+          <t>1.27,45</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -14796,7 +14971,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -14818,25 +14993,25 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Line Steine Bertelsen</t>
+          <t>Isabella Johanne Debik</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1.27,70</t>
+          <t>1.27,48</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>23.10.2021</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -14853,25 +15028,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Alice Sophie Mittet</t>
+          <t>Line Steine Bertelsen</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1.28,09</t>
+          <t>1.27,70</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>20.05.2017</t>
+          <t>23.10.2021</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -14888,20 +15063,20 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Julie Hegvik</t>
+          <t>Alice Sophie Mittet</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1.28,69</t>
+          <t>1.28,09</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>24.06.2007</t>
+          <t>20.05.2017</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -14923,20 +15098,20 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sigrid Eldholm</t>
+          <t>Julie Hegvik</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1.28,97</t>
+          <t>1.28,69</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>19.01.2019</t>
+          <t>24.06.2007</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -14958,12 +15133,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Hilde Stene Rygh</t>
+          <t>Sigrid Eldholm</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1.29,06</t>
+          <t>1.28,97</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -14971,12 +15146,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>10.03.2012</t>
+          <t>19.01.2019</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -14993,25 +15168,25 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Elise Øystrøm Tyvold</t>
+          <t>Hilde Stene Rygh</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1.29,54</t>
+          <t>1.29,06</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>10.03.2012</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -15028,20 +15203,20 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Nicole Kulagina</t>
+          <t>Elise Øystrøm Tyvold</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1.30,22</t>
+          <t>1.29,54</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -15063,25 +15238,25 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Helle Lundgren</t>
+          <t>Nicole Kulagina</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1.30,38</t>
+          <t>1.30,22</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>21.10.2023</t>
+          <t>18.01.2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -15098,12 +15273,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ingrid Johansen</t>
+          <t>Helle Lundgren</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1.30,31</t>
+          <t>1.30,38</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -15111,12 +15286,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>26.01.2007</t>
+          <t>21.10.2023</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -15133,25 +15308,25 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Helene Marie Haram</t>
+          <t>Ingrid Johansen</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1.30,43</t>
+          <t>1.30,31</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>26.10.2019</t>
+          <t>26.01.2007</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -15168,25 +15343,25 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Pia Helena Wildhagen</t>
+          <t>Helene Marie Haram</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1.30,63</t>
+          <t>1.30,43</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>16.06.2018</t>
+          <t>26.10.2019</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -15203,25 +15378,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Chloe Branlat</t>
+          <t>Pia Helena Wildhagen</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1.31,01</t>
+          <t>1.30,63</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>16.06.2018</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -15238,25 +15413,25 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Aurora Alexandra Bjordal</t>
+          <t>Chloe Branlat</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1.31,53</t>
+          <t>1.31,01</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>18.01.2020</t>
+          <t>15.02.2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -15273,20 +15448,20 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Aurora S. Juel</t>
+          <t>Aurora Alexandra Bjordal</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1.31,96</t>
+          <t>1.31,53</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>06.10.2012</t>
+          <t>18.01.2020</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -15308,20 +15483,20 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Hansine Rindberg Monsø</t>
+          <t>Aurora S. Juel</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1.32,39</t>
+          <t>1.31,96</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>19.03.2023</t>
+          <t>06.10.2012</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -15343,20 +15518,20 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Michaela Josefin Abeleva Barrera</t>
+          <t>Hansine Rindberg Monsø</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1.32,53</t>
+          <t>1.32,39</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>19.03.2023</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -15378,20 +15553,20 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Izabele Farias Ribeiro</t>
+          <t>Michaela Josefin Abeleva Barrera</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1.32,66</t>
+          <t>1.32,53</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>17.01.2014</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -15413,25 +15588,25 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ida Fiskaa Barstad</t>
+          <t>Izabele Farias Ribeiro</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1.33,00</t>
+          <t>1.32,66</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>24.10.2020</t>
+          <t>17.01.2014</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -15448,12 +15623,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Camila Dorao</t>
+          <t>Ida Fiskaa Barstad</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1.33,07</t>
+          <t>1.33,00</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -15461,12 +15636,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>24.10.2020</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -15483,20 +15658,20 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Selma Strandjord Lillerødvann</t>
+          <t>Camila Dorao</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1.33,12</t>
+          <t>1.33,07</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>27.01.2024</t>
+          <t>26.04.2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -15518,25 +15693,25 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ingrid Lianes</t>
+          <t>Selma Strandjord Lillerødvann</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1.33,61</t>
+          <t>1.33,12</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>23.05.2009</t>
+          <t>27.01.2024</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -15553,25 +15728,25 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sofia Bjørklund Mora</t>
+          <t>Ingrid Lianes</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1.33,80</t>
+          <t>1.33,61</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>15.09.2013</t>
+          <t>23.05.2009</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -15588,25 +15763,25 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Amalie Solvoll</t>
+          <t>Sofia Bjørklund Mora</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1.33,94</t>
+          <t>1.33,80</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>27.04.2019</t>
+          <t>15.09.2013</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -15623,25 +15798,25 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Inga Victoria Kirabo Nygård</t>
+          <t>Amalie Solvoll</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1.34,42</t>
+          <t>1.33,94</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>02.04.2022</t>
+          <t>27.04.2019</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -15658,25 +15833,25 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ola vatn Gundersen</t>
+          <t>Inga Victoria Kirabo Nygård</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1.23,47</t>
+          <t>1.34,42</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>16.06.2018</t>
+          <t>02.04.2022</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -15728,25 +15903,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Susanne Kolloen</t>
+          <t>Ola vatn Gundersen</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1.34,91</t>
+          <t>1.23,47</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>26.10.2019</t>
+          <t>16.06.2018</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -15763,25 +15938,25 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Emilie Sandvik Gangåssæter</t>
+          <t>Susanne Kolloen</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1.35,55</t>
+          <t>1.34,91</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>23.06.2019</t>
+          <t>26.10.2019</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -15833,20 +16008,20 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Elsa Dragsten Wake</t>
+          <t>Emilie Sandvik Gangåssæter</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1.36,62</t>
+          <t>1.35,55</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>23.06.2019</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -15868,20 +16043,20 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Nora Elvira Wengstad Jakobsen</t>
+          <t>Elsa Dragsten Wake</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1.36,87</t>
+          <t>1.36,62</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>08.12.2024</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -15903,20 +16078,20 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Ane Hegland</t>
+          <t>Nora Elvira Wengstad Jakobsen</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1.37,93</t>
+          <t>1.36,87</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -15938,20 +16113,20 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ronja Emilia Wikström</t>
+          <t>Ane Hegland</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1.38,02</t>
+          <t>1.37,93</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>27.04.2024</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -15973,20 +16148,20 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Erle Kullerud Ytrehus</t>
+          <t>Ronja Emilia Wikström</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1.38,89</t>
+          <t>1.38,02</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>27.01.2024</t>
+          <t>27.04.2024</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -16008,25 +16183,25 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Emma Nedeea Hagen</t>
+          <t>Erle Kullerud Ytrehus</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1.39,06</t>
+          <t>1.38,89</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>12.02.2022</t>
+          <t>27.01.2024</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -16043,25 +16218,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Marie Wærnes Blom</t>
+          <t>Emma Nedeea Hagen</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1.40,34</t>
+          <t>1.39,06</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>12.02.2022</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -16078,20 +16253,20 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Julia Tan</t>
+          <t>Marie Wærnes Blom</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1.41,05</t>
+          <t>1.40,34</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20.06.2009</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -16113,20 +16288,20 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Elina Arefjord Spangelo</t>
+          <t>Julia Tan</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1.41,24</t>
+          <t>1.41,05</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>20.06.2009</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -16148,20 +16323,20 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Synnøve Fevang</t>
+          <t>Elina Arefjord Spangelo</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1.41,43</t>
+          <t>1.41,24</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>05.02.2006</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -16183,25 +16358,25 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Magne Petersen</t>
+          <t>Synnøve Fevang</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1.29,86</t>
+          <t>1.41,43</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>27.10.2012</t>
+          <t>05.02.2006</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -16218,25 +16393,25 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Frida Merethe Norli Eidsvåg</t>
+          <t>Hedda Gätzschmann</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1.43,13</t>
+          <t>1.40,18</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -16253,25 +16428,25 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Hedda Gätzschmann</t>
+          <t>Magne Petersen</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1.43,45</t>
+          <t>1.29,86</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>27.10.2012</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -16288,25 +16463,25 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Lea almaas</t>
+          <t>Frida Merethe Norli Eidsvåg</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1.43,77</t>
+          <t>1.43,13</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>11.02.2012</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -16323,25 +16498,25 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Louise Thys</t>
+          <t>Lea almaas</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1.45,25</t>
+          <t>1.43,77</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>11.02.2012</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -16358,25 +16533,25 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Kaia Winnberg</t>
+          <t>Louise Thys</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1.45,56</t>
+          <t>1.45,25</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>01.12.2024</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -16393,25 +16568,25 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sigrid Gylseth Dahl</t>
+          <t>Kaia Winnberg</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1.48,11</t>
+          <t>1.45,56</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>01.12.2024</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -16428,25 +16603,25 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Madeleine Tran Wæraas</t>
+          <t>Sigrid Gylseth Dahl</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1.49,27</t>
+          <t>1.48,11</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>19.01.2019</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -16463,25 +16638,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Olivia Hjelmeseth Larsen</t>
+          <t>Live Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1.51,37</t>
+          <t>1.46,91</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>19.11.2022</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -16498,20 +16673,20 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Nicoline Vinje</t>
+          <t>Madeleine Tran Wæraas</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1.51,84</t>
+          <t>1.49,27</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>19.01.2019</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -16533,20 +16708,20 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Ella Katrine Lind Bøckman</t>
+          <t>Olivia Hjelmeseth Larsen</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1.51,91</t>
+          <t>1.51,37</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>19.11.2022</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -16568,25 +16743,25 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ingrid Skye Naustvoll</t>
+          <t>Nicoline Vinje</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1.52,24</t>
+          <t>1.51,84</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>24.11.2012</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -16603,20 +16778,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Lena Sofie Hammer</t>
+          <t>Ella Katrine Lind Bøckman</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1.53,19</t>
+          <t>1.51,91</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>18.09.2005</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -16638,25 +16813,25 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ina Birgitte Eidsmo Hova</t>
+          <t>Ingrid Skye Naustvoll</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1.54,60</t>
+          <t>1.52,24</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>18.01.2025</t>
+          <t>24.11.2012</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -16673,20 +16848,20 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Jassmitha Ajeethsing</t>
+          <t>Lena Sofie Hammer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1.54,83</t>
+          <t>1.53,19</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>19.06.2021</t>
+          <t>18.09.2005</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -16708,25 +16883,25 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Marita Fuglestad Løkken</t>
+          <t>Sara Olea  Riseth Moe</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1.54,84</t>
+          <t>1.51,93</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>09.11.2013</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -16743,20 +16918,20 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Charlotte Talseth</t>
+          <t>Ina Birgitte Eidsmo Hova</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1.54,98</t>
+          <t>1.54,60</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>18.01.2025</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -16778,25 +16953,25 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Sara Olea  Riseth Moe</t>
+          <t>Jassmitha Ajeethsing</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>1.55,22</t>
+          <t>1.54,83</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>19.06.2021</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -16813,20 +16988,20 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Nora Grande Bjerkan</t>
+          <t>Marita Fuglestad Løkken</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1.55,69</t>
+          <t>1.54,84</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>15.05.2010</t>
+          <t>09.11.2013</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -16848,20 +17023,20 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Tora Tveiten</t>
+          <t>Charlotte Talseth</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1.56,22</t>
+          <t>1.53,05</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>03.11.2012</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -16883,20 +17058,20 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Ramona Vutudal</t>
+          <t>Oda Brennhaug Tangen</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1.56,36</t>
+          <t>1.52,99</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>21.06.2008</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -16918,25 +17093,25 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Hedda Thorgaard</t>
+          <t>Nora Grande Bjerkan</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1.56,84</t>
+          <t>1.55,69</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>15.05.2010</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -16953,20 +17128,20 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sunniva Eldholm</t>
+          <t>Tora Tveiten</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1.57,65</t>
+          <t>1.56,22</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>03.11.2012</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -16988,20 +17163,20 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Anna Fenstad Høysæter</t>
+          <t>Ramona Vutudal</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>1.59,84</t>
+          <t>1.56,36</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>21.06.2008</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -17023,25 +17198,25 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Julie Gilbu</t>
+          <t>Hedda Thorgaard</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2.00,22</t>
+          <t>1.56,84</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>14.03.2015</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -17058,25 +17233,25 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Mia Bretun Finserå</t>
+          <t>Sunniva Eldholm</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>1.59,97</t>
+          <t>1.57,65</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>03.12.2011</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -17093,25 +17268,25 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Live Furmyr Johansen</t>
+          <t>Anna Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2.00,59</t>
+          <t>1.59,84</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>05.12.2021</t>
+          <t>17.11.2019</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -17128,25 +17303,25 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ida Fjellvær</t>
+          <t>Julie Gilbu</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2.02,71</t>
+          <t>2.00,22</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>18.04.2009</t>
+          <t>14.03.2015</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -17163,25 +17338,25 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Malin Sandstad</t>
+          <t>Mia Bretun Finserå</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2.02,50</t>
+          <t>1.59,97</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20.06.2009</t>
+          <t>03.12.2011</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -17198,20 +17373,20 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Aurora Dahl Bere</t>
+          <t>Kristina Kulagina</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2.02,70</t>
+          <t>1.58,64</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>06.04.2024</t>
+          <t>30.11.2025</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -17233,25 +17408,25 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Saiyara Jalisa Rahman</t>
+          <t>Live Furmyr Johansen</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2.02,67</t>
+          <t>2.00,59</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>19.09.2020</t>
+          <t>05.12.2021</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -17268,25 +17443,25 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Regine Nysæther</t>
+          <t>Ida Fjellvær</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2.04,26</t>
+          <t>2.02,71</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>31.10.2009</t>
+          <t>18.04.2009</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -17303,20 +17478,20 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Live Eilertsen-Granbo</t>
+          <t>Saiyara Jalisa Rahman</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2.04,49</t>
+          <t>2.02,67</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>15.09.2018</t>
+          <t>19.09.2020</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -17338,25 +17513,25 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Ilaria Kari Cherubini</t>
+          <t>Aurora Dahl Bere</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2.06,76</t>
+          <t>2.02,70</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>06.04.2024</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -17373,20 +17548,20 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Vilma Granhus Følstad</t>
+          <t>Malin Sandstad</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2.10,64</t>
+          <t>2.02,50</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>20.06.2009</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -17408,25 +17583,25 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Kristine Haram Bye</t>
+          <t>Ilaria Kari Cherubini</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2.10,77</t>
+          <t>2.01,72</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>04.12.2010</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -17443,25 +17618,25 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Emma Hilmarsen</t>
+          <t>Regine Nysæther</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2.11,38</t>
+          <t>2.04,26</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>02.02.2013</t>
+          <t>31.10.2009</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -17478,20 +17653,20 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Oda Emilie Krogh</t>
+          <t>Live Eilertsen-Granbo</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2.12,51</t>
+          <t>2.04,49</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>15.09.2018</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -17513,20 +17688,20 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Karolina Kania</t>
+          <t>Emilie Magnussen</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2.12,89</t>
+          <t>2.03,30</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -17548,20 +17723,20 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Klara Marie Gildemyn Strabac</t>
+          <t>Vilma Granhus Følstad</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2.13,92</t>
+          <t>2.10,64</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>17.11.2019</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -17583,25 +17758,25 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Phoebe Thalberg Fagerheim</t>
+          <t>Kristine Haram Bye</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2.20,42</t>
+          <t>2.10,77</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>18.06.2011</t>
+          <t>04.12.2010</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -17618,25 +17793,25 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Snorre Risholt Moen</t>
+          <t>Emma Hilmarsen</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2.07,54</t>
+          <t>2.11,38</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>15.09.2013</t>
+          <t>02.02.2013</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -17653,33 +17828,243 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
+          <t>Oda Emilie Krogh</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2.12,51</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>71</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>02.10.2021</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Karolina Kania</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2.12,89</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>70</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>02.10.2021</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Klara Marie Gildemyn Strabac</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2.13,92</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>68</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>17.11.2019</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Shiva Sattanathan</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2.00,05</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>65</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>30.11.2025</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Phoebe Thalberg Fagerheim</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2.20,42</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>59</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>18.06.2011</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Snorre Risholt Moen</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2.07,54</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>54</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>15.09.2013</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
           <t>KARIANNE HUSBY</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>2.26,76</t>
         </is>
       </c>
-      <c r="C188" t="n">
+      <c r="C194" t="n">
         <v>52</v>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>13.11.2010</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>Hommelvik</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
